--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE1167F-B04F-40E6-B755-712DE2FE0ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE2E95-F00F-425C-AE89-A258C20FEB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="4545" yWindow="3765" windowWidth="21600" windowHeight="12645" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>2 projects; shares gas-turbine supply chain</t>
+  </si>
+  <si>
+    <t>Update 2026-09-24 (solar PV): Share of Cost Effective Capacity Built in a Single Year for solar PV set to 0.5 in all years (deployed CSV had carried 0.75 since the 2026-09-11 calibration while this workbook still showed 1.0; both now 0.5). Rationale: at 0.75 the economic channel added 38-45 GW/yr of solar in 2027-2029 on top of the mandated pipeline (52/47/42 GW/yr total; 2030 capacity 360 GW) against ICF's forecast of 34-39 GW/yr and 2025's record ~30 GW, with solar curtailment of 53-57 TWh/yr. At 0.5, additions are 41/32/28 GW/yr and 2030 capacity 313 GW, between ReEDS StdScen24 Mid (~330) and Rhodium TS2026 Mid (262). Same 'reflect real-world builds' logic as the onshore wind values. Decision: Megan, 2026-09-24. A post-2030 dip in economic solar (profitability saturation via the CSC saturation parameter) is unaffected by this share.</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>About!$C$25:$C$125</c:f>
+              <c:f>About!$C$27:$C$127</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
@@ -796,7 +799,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>About!$B$25:$B$125</c:f>
+              <c:f>About!$B$27:$B$127</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
@@ -1862,13 +1865,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>484003</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>184356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>5052459</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>171656</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2194,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
@@ -2250,1257 +2253,1240 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17">
-        <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B20">
-        <v>30000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B21">
+      <c r="B23">
         <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <f>(1-EXP(-((C24/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25">
-        <f t="shared" ref="B25:B88" si="0">(1-EXP(-((C25/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>4.286648162477036E-6</v>
-      </c>
-      <c r="C25">
-        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>3.4290612860687911E-5</v>
+        <f>(1-EXP(-((C26/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27">
-        <f t="shared" si="0"/>
-        <v>1.1570725740235322E-4</v>
+        <f t="shared" ref="B27:B90" si="0">(1-EXP(-((C27/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>4.286648162477036E-6</v>
       </c>
       <c r="C27">
-        <f>C26+500</f>
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>2.7416034086391594E-4</v>
+        <v>3.4290612860687911E-5</v>
       </c>
       <c r="C28">
-        <f t="shared" ref="C28:C91" si="1">C27+500</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>5.3511960071055413E-4</v>
+        <v>1.1570725740235322E-4</v>
       </c>
       <c r="C29">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f>C28+500</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>9.2378588268478008E-4</v>
+        <v>2.7416034086391594E-4</v>
       </c>
       <c r="C30">
-        <f t="shared" si="1"/>
-        <v>3000</v>
+        <f t="shared" ref="C30:C93" si="1">C29+500</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>1.4649445766562463E-3</v>
+        <v>5.3511960071055413E-4</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>2.1827885823227922E-3</v>
+        <v>9.2378588268478008E-4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>3.1007125989183093E-3</v>
+        <v>1.4649445766562463E-3</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>4500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>4.2410811978808027E-3</v>
+        <v>2.1827885823227922E-3</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>5.6249738820245872E-3</v>
+        <v>3.1007125989183093E-3</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>5500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>7.2719111397427484E-3</v>
+        <v>4.2410811978808027E-3</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>9.1995663437769003E-3</v>
+        <v>5.6249738820245872E-3</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>6500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>1.1423469191788382E-2</v>
+        <v>7.2719111397427484E-3</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>1.3956707206263963E-2</v>
+        <v>9.1995663437769003E-3</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>7500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>1.6809632565965439E-2</v>
+        <v>1.1423469191788382E-2</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>1.9989582188770449E-2</v>
+        <v>1.3956707206263963E-2</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>8500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>2.3500619483080909E-2</v>
+        <v>1.6809632565965439E-2</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>2.7343306488591249E-2</v>
+        <v>1.9989582188770449E-2</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>9500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>3.1514515195616613E-2</v>
+        <v>2.3500619483080909E-2</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>3.6007286628151627E-2</v>
+        <v>2.7343306488591249E-2</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>4.0810745768913415E-2</v>
+        <v>3.1514515195616613E-2</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>11000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>4.5910079573753593E-2</v>
+        <v>3.6007286628151627E-2</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>11500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>5.1286584158818753E-2</v>
+        <v>4.0810745768913415E-2</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>5.6917785751641151E-2</v>
+        <v>4.5910079573753593E-2</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>12500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>6.2777638197790697E-2</v>
+        <v>5.1286584158818753E-2</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
-        <v>13000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>6.8836797745699688E-2</v>
+        <v>5.6917785751641151E-2</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>13500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>7.506297354898428E-2</v>
+        <v>6.2777638197790697E-2</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>14000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>8.142134989988481E-2</v>
+        <v>6.8836797745699688E-2</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
-        <v>14500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>8.787507372604586E-2</v>
+        <v>7.506297354898428E-2</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>15000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>9.438579844442066E-2</v>
+        <v>8.142134989988481E-2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
-        <v>15500</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>0.10091427297723279</v>
+        <v>8.787507372604586E-2</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>16000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>0.10742096270522571</v>
+        <v>9.438579844442066E-2</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>16500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>0.11386668746965854</v>
+        <v>0.10091427297723279</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
-        <v>17000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>0.12021326053442474</v>
+        <v>0.10742096270522571</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>17500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>0.12642411176571153</v>
+        <v>0.11386668746965854</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
-        <v>18000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>0.1324648782399141</v>
+        <v>0.12021326053442474</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>18500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>0.1383039460856948</v>
+        <v>0.12642411176571153</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>19000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>0.1439129286073208</v>
+        <v>0.1324648782399141</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
-        <v>19500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>0.14926706759510625</v>
+        <v>0.1383039460856948</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>20000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>0.15434554714316789</v>
+        <v>0.1439129286073208</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>20500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>0.1591317121715517</v>
+        <v>0.14926706759510625</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>21000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>0.16361318706836692</v>
+        <v>0.15434554714316789</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>21500</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>0.16778189328550838</v>
+        <v>0.1591317121715517</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>0.17163396818253152</v>
+        <v>0.16361318706836692</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>22500</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>0.17516959075587743</v>
+        <v>0.16778189328550838</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
-        <v>23000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>0.17839272295802988</v>
+        <v>0.17163396818253152</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>23500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>0.18131077796047496</v>
+        <v>0.17516959075587743</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <f t="shared" si="0"/>
-        <v>0.18393422882553601</v>
+        <v>0.17839272295802988</v>
       </c>
       <c r="C73">
         <f t="shared" si="1"/>
-        <v>24500</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <f t="shared" si="0"/>
-        <v>0.18627617253555084</v>
+        <v>0.18131077796047496</v>
       </c>
       <c r="C74">
         <f t="shared" si="1"/>
-        <v>25000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
         <f t="shared" si="0"/>
-        <v>0.18835186512938695</v>
+        <v>0.18393422882553601</v>
       </c>
       <c r="C75">
         <f t="shared" si="1"/>
-        <v>25500</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <f t="shared" si="0"/>
-        <v>0.19017824380056211</v>
+        <v>0.18627617253555084</v>
       </c>
       <c r="C76">
         <f t="shared" si="1"/>
-        <v>26000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <f t="shared" si="0"/>
-        <v>0.19177345124178691</v>
+        <v>0.18835186512938695</v>
       </c>
       <c r="C77">
         <f t="shared" si="1"/>
-        <v>26500</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <f t="shared" si="0"/>
-        <v>0.1931563763376668</v>
+        <v>0.19017824380056211</v>
       </c>
       <c r="C78">
         <f t="shared" si="1"/>
-        <v>27000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>0.19434622360232301</v>
+        <v>0.19177345124178691</v>
       </c>
       <c r="C79">
         <f t="shared" si="1"/>
-        <v>27500</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>0.19536212164822028</v>
+        <v>0.1931563763376668</v>
       </c>
       <c r="C80">
         <f t="shared" si="1"/>
-        <v>28000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>0.19622277858911699</v>
+        <v>0.19434622360232301</v>
       </c>
       <c r="C81">
         <f t="shared" si="1"/>
-        <v>28500</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>0.19694618976330103</v>
+        <v>0.19536212164822028</v>
       </c>
       <c r="C82">
         <f t="shared" si="1"/>
-        <v>29000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>0.19754940065027685</v>
+        <v>0.19622277858911699</v>
       </c>
       <c r="C83">
         <f t="shared" si="1"/>
-        <v>29500</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>0.19804832547095644</v>
+        <v>0.19694618976330103</v>
       </c>
       <c r="C84">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>0.19845761981600954</v>
+        <v>0.19754940065027685</v>
       </c>
       <c r="C85">
         <f t="shared" si="1"/>
-        <v>30500</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>0.19879060382342864</v>
+        <v>0.19804832547095644</v>
       </c>
       <c r="C86">
         <f t="shared" si="1"/>
-        <v>31000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>0.19905923098155251</v>
+        <v>0.19845761981600954</v>
       </c>
       <c r="C87">
         <f t="shared" si="1"/>
-        <v>31500</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>0.19927409659660289</v>
+        <v>0.19879060382342864</v>
       </c>
       <c r="C88">
         <f t="shared" si="1"/>
-        <v>32000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89">
-        <f t="shared" ref="B89:B125" si="2">(1-EXP(-((C89/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>0.19944447933595111</v>
+        <f t="shared" si="0"/>
+        <v>0.19905923098155251</v>
       </c>
       <c r="C89">
         <f t="shared" si="1"/>
-        <v>32500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90">
-        <f t="shared" si="2"/>
-        <v>0.19957840901739385</v>
+        <f t="shared" si="0"/>
+        <v>0.19927409659660289</v>
       </c>
       <c r="C90">
         <f t="shared" si="1"/>
-        <v>33000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91">
-        <f t="shared" si="2"/>
-        <v>0.19968275391843365</v>
+        <f t="shared" ref="B91:B127" si="2">(1-EXP(-((C91/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>0.19944447933595111</v>
       </c>
       <c r="C91">
         <f t="shared" si="1"/>
-        <v>33500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>0.19976332127118276</v>
+        <v>0.19957840901739385</v>
       </c>
       <c r="C92">
-        <f t="shared" ref="C92:C125" si="3">C91+500</f>
-        <v>34000</v>
+        <f t="shared" si="1"/>
+        <v>33000</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>0.19982496522253218</v>
+        <v>0.19968275391843365</v>
       </c>
       <c r="C93">
-        <f t="shared" si="3"/>
-        <v>34500</v>
+        <f t="shared" si="1"/>
+        <v>33500</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>0.19987169730697774</v>
+        <v>0.19976332127118276</v>
       </c>
       <c r="C94">
-        <f t="shared" si="3"/>
-        <v>35000</v>
+        <f t="shared" ref="C94:C127" si="3">C93+500</f>
+        <v>34000</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>0.19990679533419684</v>
+        <v>0.19982496522253218</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
-        <v>35500</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>0.1999329074744195</v>
+        <v>0.19987169730697774</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>36000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>0.19995214918026516</v>
+        <v>0.19990679533419684</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>36500</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>0.19996619137347427</v>
+        <v>0.1999329074744195</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
-        <v>37000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>0.19997633902006273</v>
+        <v>0.19995214918026516</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>37500</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>0.19998359980055544</v>
+        <v>0.19996619137347427</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
-        <v>38000</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>0.19998874304618811</v>
+        <v>0.19997633902006273</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>0.19999234945911523</v>
+        <v>0.19998359980055544</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>39000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>0.19999485237326678</v>
+        <v>0.19998874304618811</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
-        <v>39500</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>0.1999965714557792</v>
+        <v>0.19999234945911523</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>0.19999773981279137</v>
+        <v>0.19999485237326678</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
-        <v>40500</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>0.19999852546471561</v>
+        <v>0.1999965714557792</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>41000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107">
         <f t="shared" si="2"/>
-        <v>0.19999904811129313</v>
+        <v>0.19999773981279137</v>
       </c>
       <c r="C107">
         <f t="shared" si="3"/>
-        <v>41500</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108">
         <f t="shared" si="2"/>
-        <v>0.19999939203080119</v>
+        <v>0.19999852546471561</v>
       </c>
       <c r="C108">
         <f t="shared" si="3"/>
-        <v>42000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109">
         <f t="shared" si="2"/>
-        <v>0.19999961586354192</v>
+        <v>0.19999904811129313</v>
       </c>
       <c r="C109">
         <f t="shared" si="3"/>
-        <v>42500</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110">
         <f t="shared" si="2"/>
-        <v>0.19999975992763294</v>
+        <v>0.19999939203080119</v>
       </c>
       <c r="C110">
         <f t="shared" si="3"/>
-        <v>43000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111">
         <f t="shared" si="2"/>
-        <v>0.19999985161306397</v>
+        <v>0.19999961586354192</v>
       </c>
       <c r="C111">
         <f t="shared" si="3"/>
-        <v>43500</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112">
         <f t="shared" si="2"/>
-        <v>0.19999990930357772</v>
+        <v>0.19999975992763294</v>
       </c>
       <c r="C112">
         <f t="shared" si="3"/>
-        <v>44000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113">
         <f t="shared" si="2"/>
-        <v>0.19999994518873965</v>
+        <v>0.19999985161306397</v>
       </c>
       <c r="C113">
         <f t="shared" si="3"/>
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114">
         <f t="shared" si="2"/>
-        <v>0.19999996725245739</v>
+        <v>0.19999990930357772</v>
       </c>
       <c r="C114">
         <f t="shared" si="3"/>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115">
         <f t="shared" si="2"/>
-        <v>0.19999998065979441</v>
+        <v>0.19999994518873965</v>
       </c>
       <c r="C115">
         <f t="shared" si="3"/>
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116">
         <f t="shared" si="2"/>
-        <v>0.19999998871085503</v>
+        <v>0.19999996725245739</v>
       </c>
       <c r="C116">
         <f t="shared" si="3"/>
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117">
         <f t="shared" si="2"/>
-        <v>0.19999999348787459</v>
+        <v>0.19999998065979441</v>
       </c>
       <c r="C117">
         <f t="shared" si="3"/>
-        <v>46500</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118">
         <f t="shared" si="2"/>
-        <v>0.19999999628815057</v>
+        <v>0.19999998871085503</v>
       </c>
       <c r="C118">
         <f t="shared" si="3"/>
-        <v>47000</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119">
         <f t="shared" si="2"/>
-        <v>0.19999999790970302</v>
+        <v>0.19999999348787459</v>
       </c>
       <c r="C119">
         <f t="shared" si="3"/>
-        <v>47500</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120">
         <f t="shared" si="2"/>
-        <v>0.19999999883716038</v>
+        <v>0.19999999628815057</v>
       </c>
       <c r="C120">
         <f t="shared" si="3"/>
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121">
         <f t="shared" si="2"/>
-        <v>0.19999999936104543</v>
+        <v>0.19999999790970302</v>
       </c>
       <c r="C121">
         <f t="shared" si="3"/>
-        <v>48500</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47500</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122">
         <f t="shared" si="2"/>
-        <v>0.19999999965326104</v>
+        <v>0.19999999883716038</v>
       </c>
       <c r="C122">
         <f t="shared" si="3"/>
-        <v>49000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123">
         <f t="shared" si="2"/>
-        <v>0.19999999981419306</v>
+        <v>0.19999999936104543</v>
       </c>
       <c r="C123">
         <f t="shared" si="3"/>
-        <v>49500</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124">
         <f t="shared" si="2"/>
-        <v>0.19999999990169129</v>
+        <v>0.19999999965326104</v>
       </c>
       <c r="C124">
         <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125">
         <f t="shared" si="2"/>
-        <v>0.19999999994865042</v>
+        <v>0.19999999981419306</v>
       </c>
       <c r="C125">
         <f t="shared" si="3"/>
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126">
+        <f t="shared" si="2"/>
+        <v>0.19999999990169129</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127">
+        <f t="shared" si="2"/>
+        <v>0.19999999994865042</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="3"/>
         <v>50500</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>77</v>
-      </c>
-      <c r="B133" t="s">
-        <v>78</v>
-      </c>
-      <c r="C133" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>48</v>
-      </c>
-      <c r="B134">
-        <v>1300</v>
-      </c>
-      <c r="C134" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>49</v>
-      </c>
-      <c r="B135">
-        <v>600</v>
+        <v>77</v>
+      </c>
+      <c r="B135" t="s">
+        <v>78</v>
       </c>
       <c r="C135" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B136">
-        <v>10000</v>
+        <v>1300</v>
       </c>
       <c r="C136" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B137">
-        <v>2200</v>
+        <v>600</v>
       </c>
       <c r="C137" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B138">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="C138" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B139">
-        <v>15000</v>
+        <v>2200</v>
       </c>
       <c r="C139" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B140">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="C140" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B141">
-        <v>400</v>
+        <v>15000</v>
       </c>
       <c r="C141" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B142">
-        <v>500</v>
+        <v>30000</v>
       </c>
       <c r="C142" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B143">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="C143" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B144">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C144" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B145">
-        <v>5000</v>
+        <v>150</v>
       </c>
       <c r="C145" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B146">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C146" t="s">
         <v>89</v>
@@ -3508,21 +3494,21 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B147">
-        <v>2400</v>
+        <v>5000</v>
       </c>
       <c r="C147" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B148">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C148" t="s">
         <v>89</v>
@@ -3530,100 +3516,122 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B149">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="C149" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B150">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C150" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B151">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C151" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B152">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="C152" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B153">
         <v>1000</v>
       </c>
       <c r="C153" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B154">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="C154" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B155">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="C155" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B156">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C156" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>69</v>
+      </c>
+      <c r="B157">
+        <v>1200</v>
+      </c>
+      <c r="C157" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>70</v>
+      </c>
+      <c r="B158">
+        <v>400</v>
+      </c>
+      <c r="C158" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>71</v>
       </c>
-      <c r="B157">
+      <c r="B159">
         <v>800</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C159" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3683,7 +3691,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2">
-        <f>About!B16</f>
+        <f>About!B18</f>
         <v>0.2</v>
       </c>
     </row>
@@ -3692,7 +3700,7 @@
         <v>40</v>
       </c>
       <c r="B3" s="2">
-        <f>About!B17</f>
+        <f>About!B19</f>
         <v>0.6</v>
       </c>
     </row>
@@ -3701,7 +3709,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="2">
-        <f>About!B18</f>
+        <f>About!B20</f>
         <v>3</v>
       </c>
     </row>
@@ -3710,7 +3718,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="2">
-        <f>About!B19</f>
+        <f>About!B21</f>
         <v>0.5</v>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="2">
-        <f>About!B20</f>
+        <f>About!B22</f>
         <v>30000</v>
       </c>
     </row>
@@ -4348,85 +4356,85 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AB8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">

--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7F1BAE-163C-41FA-AB1B-7A3F51AD8EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE2E95-F00F-425C-AE89-A258C20FEB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="4545" yWindow="3765" windowWidth="21600" windowHeight="12645" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="CSC-CSCCCMvSoECBtY" sheetId="2" r:id="rId2"/>
-    <sheet name="CSC-CSCMBCfPTwNEC" sheetId="3" r:id="rId3"/>
+    <sheet name="CSC-CSCPH" sheetId="6" r:id="rId2"/>
+    <sheet name="CSC-CSCP" sheetId="5" r:id="rId3"/>
     <sheet name="CSC-CSCSoCECBiaSY" sheetId="4" r:id="rId4"/>
+    <sheet name="CSC-CSCSCbPT" sheetId="7" r:id="rId5"/>
+    <sheet name="CSC-ACSCSoCECBiaSY" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -47,9 +49,6 @@
     <t>These are calibrated variables used in establishing supply curves for resources.</t>
   </si>
   <si>
-    <t>Share of existing capacity</t>
-  </si>
-  <si>
     <t>Time (Year)</t>
   </si>
   <si>
@@ -137,27 +136,6 @@
     <t>Supply Curve Parameters</t>
   </si>
   <si>
-    <t>Share</t>
-  </si>
-  <si>
-    <t>parameter 1</t>
-  </si>
-  <si>
-    <t>parameter 2</t>
-  </si>
-  <si>
-    <t>max share</t>
-  </si>
-  <si>
-    <t>multiplier cutoff</t>
-  </si>
-  <si>
-    <t>Max profitability cutoff</t>
-  </si>
-  <si>
-    <t>Incremental Revenue</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
@@ -176,14 +154,200 @@
     <t>Minimum capacity buildable for plants types with no existing capacity (share if installed)</t>
   </si>
   <si>
-    <t>% of total installed capacity (tied to CSC)</t>
+    <t>cutoff parameter</t>
+  </si>
+  <si>
+    <t>saturation</t>
+  </si>
+  <si>
+    <t>scale parameter</t>
+  </si>
+  <si>
+    <t>shape parameter</t>
+  </si>
+  <si>
+    <t>location parameter</t>
+  </si>
+  <si>
+    <t>parameters</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>Multiple of annual build limit available for procurement</t>
+  </si>
+  <si>
+    <t>Headroom</t>
+  </si>
+  <si>
+    <t>Seed Capacity (MW)</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Added 2026-08 (seed redesign prototype):</t>
+  </si>
+  <si>
+    <t>CSCSCbPT CSC Seed Capacity by Plant Type - growth basis for the annual build soft cap and entry floor.</t>
+  </si>
+  <si>
+    <t>Semantics: largest recent observed annual addition (incumbent types) or typical first-project size (types never yet built).</t>
+  </si>
+  <si>
+    <t>CSCPH CSC Procurement Headroom Factor - multiple of the annual build limit available for procurement on the supply curve (keeps mandates priced on the curve interior).</t>
+  </si>
+  <si>
+    <t>ALL VALUES BELOW ARE DRAFT ENGINEERING PLACEHOLDERS - to be replaced by EIA-860-derived values per the build-cap-calibration plan.</t>
+  </si>
+  <si>
+    <t>Electricity Source</t>
+  </si>
+  <si>
+    <t>Seed (MW)</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>~2 large units; no recent US additions, legacy EPC capability</t>
+  </si>
+  <si>
+    <t>legacy type; ~2 units</t>
+  </si>
+  <si>
+    <t>recent-era max annual US additions (placeholder pending EIA-860 derivation)</t>
+  </si>
+  <si>
+    <t>one AP1000 pair (Vogtle-style)</t>
+  </si>
+  <si>
+    <t>refurbishment/small-project scale</t>
+  </si>
+  <si>
+    <t>~US record annual additions (2020)</t>
+  </si>
+  <si>
+    <t>recent utility-scale annual additions</t>
+  </si>
+  <si>
+    <t>2-3 Ivanpah-scale projects</t>
+  </si>
+  <si>
+    <t>recent max annual additions</t>
+  </si>
+  <si>
+    <t>legacy type</t>
+  </si>
+  <si>
+    <t>recent annual additions envelope</t>
+  </si>
+  <si>
+    <t>~3 concurrent lease build-outs x ~800 MW</t>
+  </si>
+  <si>
+    <t>2-3 waste-to-energy plants</t>
+  </si>
+  <si>
+    <t>2 x 500 MW first-mover capture projects</t>
+  </si>
+  <si>
+    <t>2-3 first-mover capture projects</t>
+  </si>
+  <si>
+    <t>2 x 500 MW first-mover projects</t>
+  </si>
+  <si>
+    <t>1 x 500 MW first-mover project</t>
+  </si>
+  <si>
+    <t>3-4 first-mover multi-module sites x ~300 MW</t>
+  </si>
+  <si>
+    <t>1-2 projects; shares gas-turbine supply chain</t>
+  </si>
+  <si>
+    <t>2 projects; shares gas-turbine supply chain</t>
+  </si>
+  <si>
+    <t>Update 2026-09-24 (solar PV): Share of Cost Effective Capacity Built in a Single Year for solar PV set to 0.5 in all years (deployed CSV had carried 0.75 since the 2026-09-11 calibration while this workbook still showed 1.0; both now 0.5). Rationale: at 0.75 the economic channel added 38-45 GW/yr of solar in 2027-2029 on top of the mandated pipeline (52/47/42 GW/yr total; 2030 capacity 360 GW) against ICF's forecast of 34-39 GW/yr and 2025's record ~30 GW, with solar curtailment of 53-57 TWh/yr. At 0.5, additions are 41/32/28 GW/yr and 2030 capacity 313 GW, between ReEDS StdScen24 Mid (~330) and Rhodium TS2026 Mid (262). Same 'reflect real-world builds' logic as the onshore wind values. Decision: Megan, 2026-09-24. A post-2030 dip in economic solar (profitability saturation via the CSC saturation parameter) is unaffected by this share.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +357,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -229,8 +401,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,7 +487,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>About!$C$25:$C$125</c:f>
+              <c:f>About!$C$27:$C$127</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
@@ -627,7 +799,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>About!$B$25:$B$125</c:f>
+              <c:f>About!$B$27:$B$127</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
@@ -1131,1157 +1303,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CSC-CSCCCMvSoECBtY'!$B$2:$AP$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2250</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4500</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5250</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6750</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8250</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>9750</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10500</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>12750</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>13500</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>14250</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15750</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>16500</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>17250</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>18750</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19500</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>20250</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>21000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>21750</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>22500</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>23250</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>24750</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>25500</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>26250</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>27000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>27750</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>28500</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>29250</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>30000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CSC-CSCCCMvSoECBtY'!$B$1:$AP$1</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4467069327128713E-5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.1570725740235322E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.9024377850489512E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.2378588268478008E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.8002974421282847E-3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.1007125989183093E-3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.9013271393022924E-3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.2719111397427484E-3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.0273608123333956E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.3956707206263963E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.8358395818443476E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.3500619483080909E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.9388189488745109E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.6007286628151627E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.3324507187836363E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.1286584158818753E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.982089105991404E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.8836797745699688E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.8227898345377744E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8.787507372604586E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>9.7650288683833367E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.10742096270522571</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.11705469860772776</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.12642411176571153</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.13541147940361392</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.1439129286073208</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.15184190514555035</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.1591317121715517</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.16573697488151984</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.17163396818253152</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.17681983138790913</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.18131077796047496</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.18513948060036278</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.18835186512938695</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.19100357564494788</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.1931563763376668</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.19487473347482187</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.19622277858911699</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.1972617973403015</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.19804832547095644</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5E3E-4506-B7FF-2865DFAAB582}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1627802751"/>
-        <c:axId val="1627803711"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1627802751"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1627803711"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1627803711"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1627802751"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'CSC-CSCCCMvSoECBtY'!$B$2:$AP$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1500</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2250</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4500</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5250</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6750</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8250</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>9750</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10500</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>12750</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>13500</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>14250</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15750</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>16500</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>17250</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>18750</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19500</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>20250</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>21000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>21750</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>22500</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>23250</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>24750</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>25500</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>26250</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>27000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>27750</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>28500</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>29250</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>30000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'CSC-CSCCCMvSoECBtY'!$B$1:$AP$1</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="41"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4467069327128713E-5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.1570725740235322E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.9024377850489512E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.2378588268478008E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.8002974421282847E-3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.1007125989183093E-3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.9013271393022924E-3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.2719111397427484E-3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.0273608123333956E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.3956707206263963E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.8358395818443476E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.3500619483080909E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.9388189488745109E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.6007286628151627E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.3324507187836363E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.1286584158818753E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.982089105991404E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6.8836797745699688E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7.8227898345377744E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8.787507372604586E-2</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>9.7650288683833367E-2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.10742096270522571</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.11705469860772776</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.12642411176571153</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.13541147940361392</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.1439129286073208</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.15184190514555035</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.1591317121715517</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.16573697488151984</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.17163396818253152</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.17681983138790913</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.18131077796047496</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.18513948060036278</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.18835186512938695</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.19100357564494788</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.1931563763376668</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.19487473347482187</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.19622277858911699</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.1972617973403015</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.19804832547095644</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D9CD-43DB-BDE0-8A392742F499}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1627802751"/>
-        <c:axId val="1627803711"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1627802751"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1627803711"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1627803711"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1627802751"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2837,1052 +1859,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>151130</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>484003</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>184356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>138430</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5052459</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>171656</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3890,85 +1880,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1103698-6335-5964-6586-96038B70278E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>5210175</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12E5539E-DC92-4633-8C32-ACBC3A592645}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19E926C4-5B99-77EC-1DCF-F92850905973}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4286,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
@@ -4295,17 +2206,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4318,1105 +2229,1410 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
-        <v>0.2</v>
-      </c>
-    </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17">
-        <v>0.6</v>
+      <c r="A17" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B20">
-        <v>30000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23">
         <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <f>(1-EXP(-((C24/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25">
-        <f t="shared" ref="B25:B88" si="0">(1-EXP(-((C25/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>4.286648162477036E-6</v>
-      </c>
-      <c r="C25">
-        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>3.4290612860687911E-5</v>
+        <f>(1-EXP(-((C26/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27">
-        <f t="shared" si="0"/>
-        <v>1.1570725740235322E-4</v>
+        <f t="shared" ref="B27:B90" si="0">(1-EXP(-((C27/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>4.286648162477036E-6</v>
       </c>
       <c r="C27">
-        <f>C26+500</f>
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>2.7416034086391594E-4</v>
+        <v>3.4290612860687911E-5</v>
       </c>
       <c r="C28">
-        <f t="shared" ref="C28:C91" si="1">C27+500</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>5.3511960071055413E-4</v>
+        <v>1.1570725740235322E-4</v>
       </c>
       <c r="C29">
-        <f t="shared" si="1"/>
-        <v>2500</v>
+        <f>C28+500</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>9.2378588268478008E-4</v>
+        <v>2.7416034086391594E-4</v>
       </c>
       <c r="C30">
-        <f t="shared" si="1"/>
-        <v>3000</v>
+        <f t="shared" ref="C30:C93" si="1">C29+500</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>1.4649445766562463E-3</v>
+        <v>5.3511960071055413E-4</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>2.1827885823227922E-3</v>
+        <v>9.2378588268478008E-4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>4000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>3.1007125989183093E-3</v>
+        <v>1.4649445766562463E-3</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>4500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>4.2410811978808027E-3</v>
+        <v>2.1827885823227922E-3</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>5.6249738820245872E-3</v>
+        <v>3.1007125989183093E-3</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>5500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>7.2719111397427484E-3</v>
+        <v>4.2410811978808027E-3</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>9.1995663437769003E-3</v>
+        <v>5.6249738820245872E-3</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>6500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>1.1423469191788382E-2</v>
+        <v>7.2719111397427484E-3</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>1.3956707206263963E-2</v>
+        <v>9.1995663437769003E-3</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>7500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>1.6809632565965439E-2</v>
+        <v>1.1423469191788382E-2</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>1.9989582188770449E-2</v>
+        <v>1.3956707206263963E-2</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>8500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>2.3500619483080909E-2</v>
+        <v>1.6809632565965439E-2</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>2.7343306488591249E-2</v>
+        <v>1.9989582188770449E-2</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>9500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>3.1514515195616613E-2</v>
+        <v>2.3500619483080909E-2</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>3.6007286628151627E-2</v>
+        <v>2.7343306488591249E-2</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>4.0810745768913415E-2</v>
+        <v>3.1514515195616613E-2</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>11000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>4.5910079573753593E-2</v>
+        <v>3.6007286628151627E-2</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>11500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>5.1286584158818753E-2</v>
+        <v>4.0810745768913415E-2</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>5.6917785751641151E-2</v>
+        <v>4.5910079573753593E-2</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>12500</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>6.2777638197790697E-2</v>
+        <v>5.1286584158818753E-2</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
-        <v>13000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>6.8836797745699688E-2</v>
+        <v>5.6917785751641151E-2</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>13500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>7.506297354898428E-2</v>
+        <v>6.2777638197790697E-2</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>14000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>8.142134989988481E-2</v>
+        <v>6.8836797745699688E-2</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
-        <v>14500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>8.787507372604586E-2</v>
+        <v>7.506297354898428E-2</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>15000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>9.438579844442066E-2</v>
+        <v>8.142134989988481E-2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
-        <v>15500</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>0.10091427297723279</v>
+        <v>8.787507372604586E-2</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>16000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>0.10742096270522571</v>
+        <v>9.438579844442066E-2</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>16500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>0.11386668746965854</v>
+        <v>0.10091427297723279</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
-        <v>17000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>0.12021326053442474</v>
+        <v>0.10742096270522571</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>17500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>0.12642411176571153</v>
+        <v>0.11386668746965854</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
-        <v>18000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>0.1324648782399141</v>
+        <v>0.12021326053442474</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>18500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>0.1383039460856948</v>
+        <v>0.12642411176571153</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>19000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>0.1439129286073208</v>
+        <v>0.1324648782399141</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
-        <v>19500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>0.14926706759510625</v>
+        <v>0.1383039460856948</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>20000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>0.15434554714316789</v>
+        <v>0.1439129286073208</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>20500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>0.1591317121715517</v>
+        <v>0.14926706759510625</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>21000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>0.16361318706836692</v>
+        <v>0.15434554714316789</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>21500</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>0.16778189328550838</v>
+        <v>0.1591317121715517</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>0.17163396818253152</v>
+        <v>0.16361318706836692</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>22500</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>0.17516959075587743</v>
+        <v>0.16778189328550838</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
-        <v>23000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>0.17839272295802988</v>
+        <v>0.17163396818253152</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>23500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>0.18131077796047496</v>
+        <v>0.17516959075587743</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <f t="shared" si="0"/>
-        <v>0.18393422882553601</v>
+        <v>0.17839272295802988</v>
       </c>
       <c r="C73">
         <f t="shared" si="1"/>
-        <v>24500</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <f t="shared" si="0"/>
-        <v>0.18627617253555084</v>
+        <v>0.18131077796047496</v>
       </c>
       <c r="C74">
         <f t="shared" si="1"/>
-        <v>25000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
         <f t="shared" si="0"/>
-        <v>0.18835186512938695</v>
+        <v>0.18393422882553601</v>
       </c>
       <c r="C75">
         <f t="shared" si="1"/>
-        <v>25500</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <f t="shared" si="0"/>
-        <v>0.19017824380056211</v>
+        <v>0.18627617253555084</v>
       </c>
       <c r="C76">
         <f t="shared" si="1"/>
-        <v>26000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <f t="shared" si="0"/>
-        <v>0.19177345124178691</v>
+        <v>0.18835186512938695</v>
       </c>
       <c r="C77">
         <f t="shared" si="1"/>
-        <v>26500</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <f t="shared" si="0"/>
-        <v>0.1931563763376668</v>
+        <v>0.19017824380056211</v>
       </c>
       <c r="C78">
         <f t="shared" si="1"/>
-        <v>27000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>0.19434622360232301</v>
+        <v>0.19177345124178691</v>
       </c>
       <c r="C79">
         <f t="shared" si="1"/>
-        <v>27500</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>0.19536212164822028</v>
+        <v>0.1931563763376668</v>
       </c>
       <c r="C80">
         <f t="shared" si="1"/>
-        <v>28000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>0.19622277858911699</v>
+        <v>0.19434622360232301</v>
       </c>
       <c r="C81">
         <f t="shared" si="1"/>
-        <v>28500</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>0.19694618976330103</v>
+        <v>0.19536212164822028</v>
       </c>
       <c r="C82">
         <f t="shared" si="1"/>
-        <v>29000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>0.19754940065027685</v>
+        <v>0.19622277858911699</v>
       </c>
       <c r="C83">
         <f t="shared" si="1"/>
-        <v>29500</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>0.19804832547095644</v>
+        <v>0.19694618976330103</v>
       </c>
       <c r="C84">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>0.19845761981600954</v>
+        <v>0.19754940065027685</v>
       </c>
       <c r="C85">
         <f t="shared" si="1"/>
-        <v>30500</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>0.19879060382342864</v>
+        <v>0.19804832547095644</v>
       </c>
       <c r="C86">
         <f t="shared" si="1"/>
-        <v>31000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>0.19905923098155251</v>
+        <v>0.19845761981600954</v>
       </c>
       <c r="C87">
         <f t="shared" si="1"/>
-        <v>31500</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88">
         <f t="shared" si="0"/>
-        <v>0.19927409659660289</v>
+        <v>0.19879060382342864</v>
       </c>
       <c r="C88">
         <f t="shared" si="1"/>
-        <v>32000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89">
-        <f t="shared" ref="B89:B125" si="2">(1-EXP(-((C89/$B$20-($B$19-0.5))/$B$17)^$B$18))*$B$16</f>
-        <v>0.19944447933595111</v>
+        <f t="shared" si="0"/>
+        <v>0.19905923098155251</v>
       </c>
       <c r="C89">
         <f t="shared" si="1"/>
-        <v>32500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90">
-        <f t="shared" si="2"/>
-        <v>0.19957840901739385</v>
+        <f t="shared" si="0"/>
+        <v>0.19927409659660289</v>
       </c>
       <c r="C90">
         <f t="shared" si="1"/>
-        <v>33000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91">
-        <f t="shared" si="2"/>
-        <v>0.19968275391843365</v>
+        <f t="shared" ref="B91:B127" si="2">(1-EXP(-((C91/$B$22-($B$21-0.5))/$B$19)^$B$20))*$B$18</f>
+        <v>0.19944447933595111</v>
       </c>
       <c r="C91">
         <f t="shared" si="1"/>
-        <v>33500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>0.19976332127118276</v>
+        <v>0.19957840901739385</v>
       </c>
       <c r="C92">
-        <f t="shared" ref="C92:C125" si="3">C91+500</f>
-        <v>34000</v>
+        <f t="shared" si="1"/>
+        <v>33000</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>0.19982496522253218</v>
+        <v>0.19968275391843365</v>
       </c>
       <c r="C93">
-        <f t="shared" si="3"/>
-        <v>34500</v>
+        <f t="shared" si="1"/>
+        <v>33500</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>0.19987169730697774</v>
+        <v>0.19976332127118276</v>
       </c>
       <c r="C94">
-        <f t="shared" si="3"/>
-        <v>35000</v>
+        <f t="shared" ref="C94:C127" si="3">C93+500</f>
+        <v>34000</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>0.19990679533419684</v>
+        <v>0.19982496522253218</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
-        <v>35500</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>0.1999329074744195</v>
+        <v>0.19987169730697774</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>36000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>0.19995214918026516</v>
+        <v>0.19990679533419684</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>36500</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>0.19996619137347427</v>
+        <v>0.1999329074744195</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
-        <v>37000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>0.19997633902006273</v>
+        <v>0.19995214918026516</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>37500</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>0.19998359980055544</v>
+        <v>0.19996619137347427</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
-        <v>38000</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>0.19998874304618811</v>
+        <v>0.19997633902006273</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>0.19999234945911523</v>
+        <v>0.19998359980055544</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>39000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>0.19999485237326678</v>
+        <v>0.19998874304618811</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
-        <v>39500</v>
+        <v>38500</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>0.1999965714557792</v>
+        <v>0.19999234945911523</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>0.19999773981279137</v>
+        <v>0.19999485237326678</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
-        <v>40500</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>0.19999852546471561</v>
+        <v>0.1999965714557792</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>41000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107">
         <f t="shared" si="2"/>
-        <v>0.19999904811129313</v>
+        <v>0.19999773981279137</v>
       </c>
       <c r="C107">
         <f t="shared" si="3"/>
-        <v>41500</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108">
         <f t="shared" si="2"/>
-        <v>0.19999939203080119</v>
+        <v>0.19999852546471561</v>
       </c>
       <c r="C108">
         <f t="shared" si="3"/>
-        <v>42000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109">
         <f t="shared" si="2"/>
-        <v>0.19999961586354192</v>
+        <v>0.19999904811129313</v>
       </c>
       <c r="C109">
         <f t="shared" si="3"/>
-        <v>42500</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110">
         <f t="shared" si="2"/>
-        <v>0.19999975992763294</v>
+        <v>0.19999939203080119</v>
       </c>
       <c r="C110">
         <f t="shared" si="3"/>
-        <v>43000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111">
         <f t="shared" si="2"/>
-        <v>0.19999985161306397</v>
+        <v>0.19999961586354192</v>
       </c>
       <c r="C111">
         <f t="shared" si="3"/>
-        <v>43500</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112">
         <f t="shared" si="2"/>
-        <v>0.19999990930357772</v>
+        <v>0.19999975992763294</v>
       </c>
       <c r="C112">
         <f t="shared" si="3"/>
-        <v>44000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113">
         <f t="shared" si="2"/>
-        <v>0.19999994518873965</v>
+        <v>0.19999985161306397</v>
       </c>
       <c r="C113">
         <f t="shared" si="3"/>
-        <v>44500</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114">
         <f t="shared" si="2"/>
-        <v>0.19999996725245739</v>
+        <v>0.19999990930357772</v>
       </c>
       <c r="C114">
         <f t="shared" si="3"/>
-        <v>45000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115">
         <f t="shared" si="2"/>
-        <v>0.19999998065979441</v>
+        <v>0.19999994518873965</v>
       </c>
       <c r="C115">
         <f t="shared" si="3"/>
-        <v>45500</v>
+        <v>44500</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116">
         <f t="shared" si="2"/>
-        <v>0.19999998871085503</v>
+        <v>0.19999996725245739</v>
       </c>
       <c r="C116">
         <f t="shared" si="3"/>
-        <v>46000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117">
         <f t="shared" si="2"/>
-        <v>0.19999999348787459</v>
+        <v>0.19999998065979441</v>
       </c>
       <c r="C117">
         <f t="shared" si="3"/>
-        <v>46500</v>
+        <v>45500</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118">
         <f t="shared" si="2"/>
-        <v>0.19999999628815057</v>
+        <v>0.19999998871085503</v>
       </c>
       <c r="C118">
         <f t="shared" si="3"/>
-        <v>47000</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119">
         <f t="shared" si="2"/>
-        <v>0.19999999790970302</v>
+        <v>0.19999999348787459</v>
       </c>
       <c r="C119">
         <f t="shared" si="3"/>
-        <v>47500</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120">
         <f t="shared" si="2"/>
-        <v>0.19999999883716038</v>
+        <v>0.19999999628815057</v>
       </c>
       <c r="C120">
         <f t="shared" si="3"/>
-        <v>48000</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121">
         <f t="shared" si="2"/>
-        <v>0.19999999936104543</v>
+        <v>0.19999999790970302</v>
       </c>
       <c r="C121">
         <f t="shared" si="3"/>
-        <v>48500</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122">
         <f t="shared" si="2"/>
-        <v>0.19999999965326104</v>
+        <v>0.19999999883716038</v>
       </c>
       <c r="C122">
         <f t="shared" si="3"/>
-        <v>49000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123">
         <f t="shared" si="2"/>
-        <v>0.19999999981419306</v>
+        <v>0.19999999936104543</v>
       </c>
       <c r="C123">
         <f t="shared" si="3"/>
-        <v>49500</v>
+        <v>48500</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124">
         <f t="shared" si="2"/>
-        <v>0.19999999990169129</v>
+        <v>0.19999999965326104</v>
       </c>
       <c r="C124">
         <f t="shared" si="3"/>
-        <v>50000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B125">
         <f t="shared" si="2"/>
-        <v>0.19999999994865042</v>
+        <v>0.19999999981419306</v>
       </c>
       <c r="C125">
         <f t="shared" si="3"/>
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126">
+        <f t="shared" si="2"/>
+        <v>0.19999999990169129</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B127">
+        <f t="shared" si="2"/>
+        <v>0.19999999994865042</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="3"/>
         <v>50500</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>77</v>
+      </c>
+      <c r="B135" t="s">
+        <v>78</v>
+      </c>
+      <c r="C135" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>48</v>
+      </c>
+      <c r="B136">
+        <v>1300</v>
+      </c>
+      <c r="C136" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>49</v>
+      </c>
+      <c r="B137">
+        <v>600</v>
+      </c>
+      <c r="C137" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138">
+        <v>10000</v>
+      </c>
+      <c r="C138" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>51</v>
+      </c>
+      <c r="B139">
+        <v>2200</v>
+      </c>
+      <c r="C139" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>52</v>
+      </c>
+      <c r="B140">
+        <v>500</v>
+      </c>
+      <c r="C140" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>53</v>
+      </c>
+      <c r="B141">
+        <v>15000</v>
+      </c>
+      <c r="C141" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>54</v>
+      </c>
+      <c r="B142">
+        <v>30000</v>
+      </c>
+      <c r="C142" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>55</v>
+      </c>
+      <c r="B143">
+        <v>400</v>
+      </c>
+      <c r="C143" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>56</v>
+      </c>
+      <c r="B144">
+        <v>500</v>
+      </c>
+      <c r="C144" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>57</v>
+      </c>
+      <c r="B145">
+        <v>150</v>
+      </c>
+      <c r="C145" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>58</v>
+      </c>
+      <c r="B146">
+        <v>200</v>
+      </c>
+      <c r="C146" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>59</v>
+      </c>
+      <c r="B147">
+        <v>5000</v>
+      </c>
+      <c r="C147" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>60</v>
+      </c>
+      <c r="B148">
+        <v>600</v>
+      </c>
+      <c r="C148" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>61</v>
+      </c>
+      <c r="B149">
+        <v>2400</v>
+      </c>
+      <c r="C149" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>62</v>
+      </c>
+      <c r="B150">
+        <v>200</v>
+      </c>
+      <c r="C150" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>63</v>
+      </c>
+      <c r="B151">
+        <v>200</v>
+      </c>
+      <c r="C151" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>64</v>
+      </c>
+      <c r="B152">
+        <v>100</v>
+      </c>
+      <c r="C152" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>65</v>
+      </c>
+      <c r="B153">
+        <v>1000</v>
+      </c>
+      <c r="C153" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>66</v>
+      </c>
+      <c r="B154">
+        <v>1500</v>
+      </c>
+      <c r="C154" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>67</v>
+      </c>
+      <c r="B155">
+        <v>1000</v>
+      </c>
+      <c r="C155" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>68</v>
+      </c>
+      <c r="B156">
+        <v>500</v>
+      </c>
+      <c r="C156" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>69</v>
+      </c>
+      <c r="B157">
+        <v>1200</v>
+      </c>
+      <c r="C157" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>70</v>
+      </c>
+      <c r="B158">
+        <v>400</v>
+      </c>
+      <c r="C158" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>71</v>
+      </c>
+      <c r="B159">
+        <v>800</v>
+      </c>
+      <c r="C159" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5426,718 +3642,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A8C2E7-868E-446E-8321-CDDE5386BCAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A11C1E0A-8F45-40E3-8B5E-CEBD35E65C82}">
   <sheetPr>
-    <tabColor rgb="FF002060"/>
+    <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:CF2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1">
-        <f>(1-EXP(-((B2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0</v>
-      </c>
-      <c r="C1">
-        <f>(1-EXP(-((C2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.4467069327128713E-5</v>
-      </c>
-      <c r="D1">
-        <f>(1-EXP(-((D2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.1570725740235322E-4</v>
-      </c>
-      <c r="E1">
-        <f>(1-EXP(-((E2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>3.9024377850489512E-4</v>
-      </c>
-      <c r="F1">
-        <f>(1-EXP(-((F2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>9.2378588268478008E-4</v>
-      </c>
-      <c r="G1">
-        <f>(1-EXP(-((G2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.8002974421282847E-3</v>
-      </c>
-      <c r="H1">
-        <f>(1-EXP(-((H2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>3.1007125989183093E-3</v>
-      </c>
-      <c r="I1">
-        <f>(1-EXP(-((I2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>4.9013271393022924E-3</v>
-      </c>
-      <c r="J1">
-        <f>(1-EXP(-((J2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>7.2719111397427484E-3</v>
-      </c>
-      <c r="K1">
-        <f>(1-EXP(-((K2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.0273608123333956E-2</v>
-      </c>
-      <c r="L1">
-        <f>(1-EXP(-((L2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.3956707206263963E-2</v>
-      </c>
-      <c r="M1">
-        <f>(1-EXP(-((M2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>1.8358395818443476E-2</v>
-      </c>
-      <c r="N1">
-        <f>(1-EXP(-((N2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>2.3500619483080909E-2</v>
-      </c>
-      <c r="O1">
-        <f>(1-EXP(-((O2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>2.9388189488745109E-2</v>
-      </c>
-      <c r="P1">
-        <f>(1-EXP(-((P2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>3.6007286628151627E-2</v>
-      </c>
-      <c r="Q1">
-        <f>(1-EXP(-((Q2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>4.3324507187836363E-2</v>
-      </c>
-      <c r="R1">
-        <f>(1-EXP(-((R2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>5.1286584158818753E-2</v>
-      </c>
-      <c r="S1">
-        <f>(1-EXP(-((S2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>5.982089105991404E-2</v>
-      </c>
-      <c r="T1">
-        <f>(1-EXP(-((T2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>6.8836797745699688E-2</v>
-      </c>
-      <c r="U1">
-        <f>(1-EXP(-((U2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>7.8227898345377744E-2</v>
-      </c>
-      <c r="V1">
-        <f>(1-EXP(-((V2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>8.787507372604586E-2</v>
-      </c>
-      <c r="W1">
-        <f>(1-EXP(-((W2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>9.7650288683833367E-2</v>
-      </c>
-      <c r="X1">
-        <f>(1-EXP(-((X2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.10742096270522571</v>
-      </c>
-      <c r="Y1">
-        <f>(1-EXP(-((Y2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.11705469860772776</v>
-      </c>
-      <c r="Z1">
-        <f>(1-EXP(-((Z2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.12642411176571153</v>
-      </c>
-      <c r="AA1">
-        <f>(1-EXP(-((AA2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.13541147940361392</v>
-      </c>
-      <c r="AB1">
-        <f>(1-EXP(-((AB2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1439129286073208</v>
-      </c>
-      <c r="AC1">
-        <f>(1-EXP(-((AC2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.15184190514555035</v>
-      </c>
-      <c r="AD1">
-        <f>(1-EXP(-((AD2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1591317121715517</v>
-      </c>
-      <c r="AE1">
-        <f>(1-EXP(-((AE2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.16573697488151984</v>
-      </c>
-      <c r="AF1">
-        <f>(1-EXP(-((AF2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.17163396818253152</v>
-      </c>
-      <c r="AG1">
-        <f>(1-EXP(-((AG2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.17681983138790913</v>
-      </c>
-      <c r="AH1">
-        <f>(1-EXP(-((AH2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.18131077796047496</v>
-      </c>
-      <c r="AI1">
-        <f>(1-EXP(-((AI2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.18513948060036278</v>
-      </c>
-      <c r="AJ1">
-        <f>(1-EXP(-((AJ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.18835186512938695</v>
-      </c>
-      <c r="AK1">
-        <f>(1-EXP(-((AK2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19100357564494788</v>
-      </c>
-      <c r="AL1">
-        <f>(1-EXP(-((AL2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1931563763376668</v>
-      </c>
-      <c r="AM1">
-        <f>(1-EXP(-((AM2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19487473347482187</v>
-      </c>
-      <c r="AN1">
-        <f>(1-EXP(-((AN2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19622277858911699</v>
-      </c>
-      <c r="AO1">
-        <f>(1-EXP(-((AO2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1972617973403015</v>
-      </c>
-      <c r="AP1">
-        <f>(1-EXP(-((AP2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19804832547095644</v>
-      </c>
-      <c r="AQ1">
-        <f>(1-EXP(-((AQ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19863287140923547</v>
-      </c>
-      <c r="AR1">
-        <f>(1-EXP(-((AR2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19905923098155251</v>
-      </c>
-      <c r="AS1">
-        <f>(1-EXP(-((AS2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.199364318136077</v>
-      </c>
-      <c r="AT1">
-        <f>(1-EXP(-((AT2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19957840901739385</v>
-      </c>
-      <c r="AU1">
-        <f>(1-EXP(-((AU2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1997256853595088</v>
-      </c>
-      <c r="AV1">
-        <f>(1-EXP(-((AV2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19982496522253218</v>
-      </c>
-      <c r="AW1">
-        <f>(1-EXP(-((AW2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19989052148534298</v>
-      </c>
-      <c r="AX1">
-        <f>(1-EXP(-((AX2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1999329074744195</v>
-      </c>
-      <c r="AY1">
-        <f>(1-EXP(-((AY2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19995973093159392</v>
-      </c>
-      <c r="AZ1">
-        <f>(1-EXP(-((AZ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19997633902006273</v>
-      </c>
-      <c r="BA1">
-        <f>(1-EXP(-((BA2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19998639592309114</v>
-      </c>
-      <c r="BB1">
-        <f>(1-EXP(-((BB2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999234945911523</v>
-      </c>
-      <c r="BC1">
-        <f>(1-EXP(-((BC2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999579357241226</v>
-      </c>
-      <c r="BD1">
-        <f>(1-EXP(-((BD2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999773981279137</v>
-      </c>
-      <c r="BE1">
-        <f>(1-EXP(-((BE2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999881369426081</v>
-      </c>
-      <c r="BF1">
-        <f>(1-EXP(-((BF2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999939203080119</v>
-      </c>
-      <c r="BG1">
-        <f>(1-EXP(-((BG2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999969590396702</v>
-      </c>
-      <c r="BH1">
-        <f>(1-EXP(-((BH2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999985161306397</v>
-      </c>
-      <c r="BI1">
-        <f>(1-EXP(-((BI2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999992939299016</v>
-      </c>
-      <c r="BJ1">
-        <f>(1-EXP(-((BJ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999996725245739</v>
-      </c>
-      <c r="BK1">
-        <f>(1-EXP(-((BK2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999998520210779</v>
-      </c>
-      <c r="BL1">
-        <f>(1-EXP(-((BL2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999348787459</v>
-      </c>
-      <c r="BM1">
-        <f>(1-EXP(-((BM2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999721029099</v>
-      </c>
-      <c r="BN1">
-        <f>(1-EXP(-((BN2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999883716038</v>
-      </c>
-      <c r="BO1">
-        <f>(1-EXP(-((BO2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999952857025</v>
-      </c>
-      <c r="BP1">
-        <f>(1-EXP(-((BP2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999981419306</v>
-      </c>
-      <c r="BQ1">
-        <f>(1-EXP(-((BQ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999992883505</v>
-      </c>
-      <c r="BR1">
-        <f>(1-EXP(-((BR2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999997352469</v>
-      </c>
-      <c r="BS1">
-        <f>(1-EXP(-((BS2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999043694</v>
-      </c>
-      <c r="BT1">
-        <f>(1-EXP(-((BT2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999664766</v>
-      </c>
-      <c r="BU1">
-        <f>(1-EXP(-((BU2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999886001</v>
-      </c>
-      <c r="BV1">
-        <f>(1-EXP(-((BV2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999962412</v>
-      </c>
-      <c r="BW1">
-        <f>(1-EXP(-((BW2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999987986</v>
-      </c>
-      <c r="BX1">
-        <f>(1-EXP(-((BX2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999996282</v>
-      </c>
-      <c r="BY1">
-        <f>(1-EXP(-((BY2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999998885</v>
-      </c>
-      <c r="BZ1">
-        <f>(1-EXP(-((BZ2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999999676</v>
-      </c>
-      <c r="CA1">
-        <f>(1-EXP(-((CA2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.1999999999999991</v>
-      </c>
-      <c r="CB1">
-        <f>(1-EXP(-((CB2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999999976</v>
-      </c>
-      <c r="CC1">
-        <f>(1-EXP(-((CC2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="CD1">
-        <f>(1-EXP(-((CD2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="CE1">
-        <f>(1-EXP(-((CE2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.2</v>
-      </c>
-      <c r="CF1">
-        <f>(1-EXP(-((CF2/About!$B$20-(About!$B$19-0.5))/About!$B$17)^About!$B$18))*About!$B$16</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <f>B2+750</f>
-        <v>750</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:BO2" si="0">C2+750</f>
-        <v>1500</v>
-      </c>
-      <c r="E2">
-        <f t="shared" si="0"/>
-        <v>2250</v>
-      </c>
-      <c r="F2">
-        <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
-        <v>3750</v>
-      </c>
-      <c r="H2">
-        <f t="shared" si="0"/>
-        <v>4500</v>
-      </c>
-      <c r="I2">
-        <f t="shared" si="0"/>
-        <v>5250</v>
-      </c>
-      <c r="J2">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="K2">
-        <f t="shared" si="0"/>
-        <v>6750</v>
-      </c>
-      <c r="L2">
-        <f t="shared" si="0"/>
-        <v>7500</v>
-      </c>
-      <c r="M2">
-        <f t="shared" si="0"/>
-        <v>8250</v>
-      </c>
-      <c r="N2">
-        <f t="shared" si="0"/>
-        <v>9000</v>
-      </c>
-      <c r="O2">
-        <f t="shared" si="0"/>
-        <v>9750</v>
-      </c>
-      <c r="P2">
-        <f t="shared" si="0"/>
-        <v>10500</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>11250</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="0"/>
-        <v>12000</v>
-      </c>
-      <c r="S2">
-        <f t="shared" si="0"/>
-        <v>12750</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="0"/>
-        <v>13500</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="0"/>
-        <v>14250</v>
-      </c>
-      <c r="V2">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-      <c r="W2">
-        <f t="shared" si="0"/>
-        <v>15750</v>
-      </c>
-      <c r="X2">
-        <f t="shared" si="0"/>
-        <v>16500</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>17250</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>18000</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>18750</v>
-      </c>
-      <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>19500</v>
-      </c>
-      <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>20250</v>
-      </c>
-      <c r="AD2">
-        <f t="shared" si="0"/>
-        <v>21000</v>
-      </c>
-      <c r="AE2">
-        <f t="shared" si="0"/>
-        <v>21750</v>
-      </c>
-      <c r="AF2">
-        <f t="shared" si="0"/>
-        <v>22500</v>
-      </c>
-      <c r="AG2">
-        <f t="shared" si="0"/>
-        <v>23250</v>
-      </c>
-      <c r="AH2">
-        <f t="shared" si="0"/>
-        <v>24000</v>
-      </c>
-      <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>24750</v>
-      </c>
-      <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>25500</v>
-      </c>
-      <c r="AK2">
-        <f t="shared" si="0"/>
-        <v>26250</v>
-      </c>
-      <c r="AL2">
-        <f t="shared" si="0"/>
-        <v>27000</v>
-      </c>
-      <c r="AM2">
-        <f t="shared" si="0"/>
-        <v>27750</v>
-      </c>
-      <c r="AN2">
-        <f t="shared" si="0"/>
-        <v>28500</v>
-      </c>
-      <c r="AO2">
-        <f t="shared" si="0"/>
-        <v>29250</v>
-      </c>
-      <c r="AP2">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="AQ2">
-        <f t="shared" si="0"/>
-        <v>30750</v>
-      </c>
-      <c r="AR2">
-        <f t="shared" si="0"/>
-        <v>31500</v>
-      </c>
-      <c r="AS2">
-        <f t="shared" si="0"/>
-        <v>32250</v>
-      </c>
-      <c r="AT2">
-        <f t="shared" si="0"/>
-        <v>33000</v>
-      </c>
-      <c r="AU2">
-        <f t="shared" si="0"/>
-        <v>33750</v>
-      </c>
-      <c r="AV2">
-        <f t="shared" si="0"/>
-        <v>34500</v>
-      </c>
-      <c r="AW2">
-        <f t="shared" si="0"/>
-        <v>35250</v>
-      </c>
-      <c r="AX2">
-        <f t="shared" si="0"/>
-        <v>36000</v>
-      </c>
-      <c r="AY2">
-        <f t="shared" si="0"/>
-        <v>36750</v>
-      </c>
-      <c r="AZ2">
-        <f t="shared" si="0"/>
-        <v>37500</v>
-      </c>
-      <c r="BA2">
-        <f t="shared" si="0"/>
-        <v>38250</v>
-      </c>
-      <c r="BB2">
-        <f t="shared" si="0"/>
-        <v>39000</v>
-      </c>
-      <c r="BC2">
-        <f t="shared" si="0"/>
-        <v>39750</v>
-      </c>
-      <c r="BD2">
-        <f t="shared" si="0"/>
-        <v>40500</v>
-      </c>
-      <c r="BE2">
-        <f t="shared" si="0"/>
-        <v>41250</v>
-      </c>
-      <c r="BF2">
-        <f t="shared" si="0"/>
-        <v>42000</v>
-      </c>
-      <c r="BG2">
-        <f t="shared" si="0"/>
-        <v>42750</v>
-      </c>
-      <c r="BH2">
-        <f t="shared" si="0"/>
-        <v>43500</v>
-      </c>
-      <c r="BI2">
-        <f t="shared" si="0"/>
-        <v>44250</v>
-      </c>
-      <c r="BJ2">
-        <f t="shared" si="0"/>
-        <v>45000</v>
-      </c>
-      <c r="BK2">
-        <f t="shared" si="0"/>
-        <v>45750</v>
-      </c>
-      <c r="BL2">
-        <f t="shared" si="0"/>
-        <v>46500</v>
-      </c>
-      <c r="BM2">
-        <f t="shared" si="0"/>
-        <v>47250</v>
-      </c>
-      <c r="BN2">
-        <f t="shared" si="0"/>
-        <v>48000</v>
-      </c>
-      <c r="BO2">
-        <f t="shared" si="0"/>
-        <v>48750</v>
-      </c>
-      <c r="BP2">
-        <f t="shared" ref="BP2:CE2" si="1">BO2+750</f>
-        <v>49500</v>
-      </c>
-      <c r="BQ2">
-        <f t="shared" si="1"/>
-        <v>50250</v>
-      </c>
-      <c r="BR2">
-        <f t="shared" si="1"/>
-        <v>51000</v>
-      </c>
-      <c r="BS2">
-        <f t="shared" si="1"/>
-        <v>51750</v>
-      </c>
-      <c r="BT2">
-        <f t="shared" si="1"/>
-        <v>52500</v>
-      </c>
-      <c r="BU2">
-        <f t="shared" si="1"/>
-        <v>53250</v>
-      </c>
-      <c r="BV2">
-        <f t="shared" si="1"/>
-        <v>54000</v>
-      </c>
-      <c r="BW2">
-        <f t="shared" si="1"/>
-        <v>54750</v>
-      </c>
-      <c r="BX2">
-        <f t="shared" si="1"/>
-        <v>55500</v>
-      </c>
-      <c r="BY2">
-        <f t="shared" si="1"/>
-        <v>56250</v>
-      </c>
-      <c r="BZ2">
-        <f t="shared" si="1"/>
-        <v>57000</v>
-      </c>
-      <c r="CA2">
-        <f t="shared" si="1"/>
-        <v>57750</v>
-      </c>
-      <c r="CB2">
-        <f t="shared" si="1"/>
-        <v>58500</v>
-      </c>
-      <c r="CC2">
-        <f t="shared" si="1"/>
-        <v>59250</v>
-      </c>
-      <c r="CD2">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-      <c r="CE2">
-        <f t="shared" si="1"/>
-        <v>60750</v>
-      </c>
-      <c r="CF2" s="2">
-        <v>1000000000000</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCC8EED-C1F0-46D1-887C-CF4C1E6085B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F1B329-5591-420B-9DBA-D539EDB26DE6}">
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>46</v>
+      <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="3">
-        <f>About!B21/About!B16</f>
-        <v>0.02</v>
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2">
+        <f>About!B18</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2">
+        <f>About!B19</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2">
+        <f>About!B20</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2">
+        <f>About!B21</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2">
+        <f>About!B22</f>
+        <v>30000</v>
       </c>
     </row>
   </sheetData>
@@ -6158,7 +3749,7 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2024</v>
@@ -6244,7 +3835,7 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -6330,7 +3921,7 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -6416,7 +4007,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -6502,7 +4093,7 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -6588,7 +4179,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -6674,10 +4265,10 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
         <v>0.1</v>
@@ -6695,160 +4286,160 @@
         <v>0.1</v>
       </c>
       <c r="H7">
-        <f>0.7/3+G7</f>
-        <v>0.33333333333333331</v>
+        <f>($J$7-$G$7)/3+G7</f>
+        <v>0.23333333333333334</v>
       </c>
       <c r="I7">
-        <f>0.7/3+H7</f>
-        <v>0.56666666666666665</v>
+        <f>($J$7-$G$7)/3+H7</f>
+        <v>0.3666666666666667</v>
       </c>
       <c r="J7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="N7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="P7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="S7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="T7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="U7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="V7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="X7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Y7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="Z7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AA7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AB7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AB8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -6934,7 +4525,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -7020,7 +4611,7 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -7106,7 +4697,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -7192,7 +4783,7 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7278,7 +4869,7 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -7364,7 +4955,7 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -7450,7 +5041,7 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -7536,7 +5127,7 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -7622,7 +5213,7 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -7708,7 +5299,7 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -7794,7 +5385,7 @@
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -7880,7 +5471,7 @@
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -7966,7 +5557,7 @@
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -8052,7 +5643,7 @@
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -8138,7 +5729,7 @@
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -8224,7 +5815,2380 @@
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465ADDB1-7904-4401-8251-42AFA6AB8D4E}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25">
+        <v>800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB721B6-2584-41BB-8944-107FD3869B44}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:AB25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.5</v>
+      </c>
+      <c r="I7">
+        <v>0.5</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+      <c r="M7">
+        <v>0.5</v>
+      </c>
+      <c r="N7">
+        <v>0.5</v>
+      </c>
+      <c r="O7">
+        <v>0.5</v>
+      </c>
+      <c r="P7">
+        <v>0.5</v>
+      </c>
+      <c r="Q7">
+        <v>0.5</v>
+      </c>
+      <c r="R7">
+        <v>0.5</v>
+      </c>
+      <c r="S7">
+        <v>0.5</v>
+      </c>
+      <c r="T7">
+        <v>0.5</v>
+      </c>
+      <c r="U7">
+        <v>0.5</v>
+      </c>
+      <c r="V7">
+        <v>0.5</v>
+      </c>
+      <c r="W7">
+        <v>0.5</v>
+      </c>
+      <c r="X7">
+        <v>0.5</v>
+      </c>
+      <c r="Y7">
+        <v>0.5</v>
+      </c>
+      <c r="Z7">
+        <v>0.5</v>
+      </c>
+      <c r="AA7">
+        <v>0.5</v>
+      </c>
+      <c r="AB7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
       </c>
       <c r="B25">
         <v>1</v>
